--- a/Reports/Low_Performer_Report.xlsx
+++ b/Reports/Low_Performer_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALOK </t>
+          <t>Alok</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,7 +470,7 @@
         <v>6.666666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>1.428571428571429</v>
+        <v>1.639344262295082</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mohammad Akeel</t>
+          <t>Akeel Khan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>2.857142857142857</v>
+        <v>3.278688524590164</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -504,19 +504,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jagat Kumar</t>
+          <t>Akeel khan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jagat.kumar@liet.in</t>
+          <t>mohammadakeelbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26.66666666666667</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>4.285714285714286</v>
+        <v>4.918032786885246</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -527,19 +527,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aman Kumar</t>
+          <t xml:space="preserve">Krishna Kumar Sah </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ak8102347910@gmail.com</t>
+          <t>ksah9189@gmail.com</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33.33333333333333</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="D5" t="n">
-        <v>5.714285714285714</v>
+        <v>6.557377049180328</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -550,19 +550,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Akeel khan</t>
+          <t>Sonu Kumar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mohammadakeelbtech23-27@liet.in</t>
+          <t>sonukumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>48.35164835164835</v>
       </c>
       <c r="D6" t="n">
-        <v>7.142857142857142</v>
+        <v>8.196721311475409</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -573,132 +573,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Krishna Kumar Sah</t>
+          <t xml:space="preserve">Rohit Kumar </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>krishnakumarsahbtech23-27@liet.in</t>
+          <t>rohitkumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.42857142857143</v>
+        <v>56.48854961832062</v>
       </c>
       <c r="D7" t="n">
-        <v>8.571428571428571</v>
+        <v>9.836065573770492</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sonu Kumar</t>
+          <t xml:space="preserve">Shreyanshi Yadav </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sonukumar3570357@gmail.com</t>
+          <t>yadavshreyanshi772@gmail.com</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48.35164835164835</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11.47540983606557</v>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Aman Kumar</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>amankumarbtech23-27@liet.in</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="D9" t="n">
-        <v>11.42857142857143</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>56.09756097560976</v>
-      </c>
-      <c r="D10" t="n">
-        <v>12.85714285714286</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Rohit Kumar</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>rohitkumarbtech23-27@liet.in</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>56.48854961832062</v>
-      </c>
-      <c r="D11" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Shreyanshi Yadav</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yadavshreyanshi022@gmail.com</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="D12" t="n">
-        <v>15.71428571428571</v>
-      </c>
-      <c r="E12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
